--- a/excel_files/report_2026-02-01_2026-02-28.xlsx
+++ b/excel_files/report_2026-02-01_2026-02-28.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +491,11 @@
           <t>Количество дней</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Рассечт за жилье</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -499,26 +505,29 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ООО «ГПНЭС»</t>
+          <t xml:space="preserve"> Сервис центр ЭПУ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Поцелуев А.С</t>
+          <t>Чумачкова М.С.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
@@ -529,17 +538,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ООО «ГПНЭС»</t>
+          <t>АНО ДПО "ЮУЦ"</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Галкин В.А</t>
+          <t>Афанасьева А.А.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -548,7 +557,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>5500</v>
       </c>
     </row>
     <row r="4">
@@ -559,26 +571,5969 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ООО «ГПНЭС»</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Калашников И.Н</t>
+          <t>Нигматьянов А.И.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>3</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Асылгареев М.Р.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Давыдов Д.А.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Юн В.В.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Шихалев В.И.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Колесов Ш.Р.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Талицких М.В.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Манашев Р.Ю.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Солякин С.В.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Рогачевских Ю.С.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Коваленко Е.А.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Казанцева А.А.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Жильцов Д.В.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Коновалова Е.Г.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Попов Е.А.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Ловицкий А.А.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Платонов С.В.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Логинов В.А.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Автоматизация</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Спиридонов Я.Э.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Попов М.А.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Назаров Р.Р.</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Будылдин П.С.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Дудин Л.С.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Трубинов А.С.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Купчиков Д.А.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Стишенко О.И</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Отставных А.Н.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Русаков Д.Е.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Хасанов А.А.</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Стальмаков О.В.</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Бабаев Д.Н.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Колобов С.В.</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Талынов Н.С.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Сизов И.В.</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Левин М.М.</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Звягинцев  А.В.</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Чигвинцев М.А.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Гончаров А.С.</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Яровой Д.В.</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Андреев М.А.</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Петров Д.Е.</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Малко Э.В.</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Воронецкий Д.В.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Кондрашов С.С.</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Тардаскин В.П.</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-В</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Кузнецов В.М.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-ИТО</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Филимонов К.В.</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>19.02.2026</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-ИТО</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Казанцев Д.А.</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Снабжение</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Порфирьев С.А.</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Снабжение</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Черников В.П.</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Энергосистемы</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Варламов В.А.</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Энергосистемы</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Телицын А.П.</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Энергосистемы</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Сеник У.Н.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Энергосистемы</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Власенко В.Н.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ГПН-Энергосистемы</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Шевченко С.А.</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Савин В.О.</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Шигаев Д.В.</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Купалов Д.А.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Ардашов А.Г.</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Сайнаков Д.П.</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Стальмоков О.В.</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Бурдуков А.Н.</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Шайхулов А.Р.</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Стрельченко Я.А.</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Гламозда И.В.</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Бабушкин Д.Б.</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Русаков К.Е.</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Шеверов В.В.</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Макаев И.Р.</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Дементьев Д.В.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Бабаев Н.Н.</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Быковский В.О.</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Смирнов Д.И.</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Тимофеев Е.Г.</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Сидоренко О.В.</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Быконя Т.В.</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Дорошкевич К.Ю.</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Филончук Г.В.</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Кондратьев О.А.</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Артемов В.В.</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Сахно М.Ю.</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Кунин М.И.</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Зандер Д.Э.</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Мельникова Н.С.</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>14.02.2026</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Швецов В.Ю.</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Курбатов С.С.</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Дорошкевич К.Ю.</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Кутлияров А.П.</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>09.02.2026</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Миселев Н.П.</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Замойский А.А.</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Былинка П.А.</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Миронов Д.Н.</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Савинский С.В.</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Якушин А.В.</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Кутлияров А.П.</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>09.02.2026</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Ряполов Б.Н</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Зозуля Ю.А.</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Ганеев А.Р.</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Чудиновский А.О.</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Самойлов Н.В.</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Бичан М.В.</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Николаев В.В.</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Шахмаев А.И.</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Орлов П.Д.</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Редько В.В.</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>02.02.2026</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Жидков А.В.</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Москвин В.В.</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Фролов М.В.</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Никитина Н.Л.</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>14.02.2026</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Шакин Ю.А.</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Школин К.М.</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Бурыхина К.К.</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>14.02.2026</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Федоров А.С.</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Гарифуллин А.Ф.</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Корнеев П.О.</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Королева В.В.</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Котова т.В.</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Казакова Э.Ф.</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Нестеров Н.Ю.</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Ильина А.М.</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Мамец А.С.</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Ярчинский Д.П.</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Третьяков А.В.</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Кычиков А.М.</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>02.02.2026</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Сулимский Д.М.</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>16.02.2026</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>19.02.2026</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Малахов П.В.</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Мишин В.А.</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Худорожко А.С.</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Терентьев Д.А.</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Черепанов И.В.</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Тимощенко Д.А.</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Попов А.А.</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Сорокин А.А.</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Кусков А.Ю.</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Шаталов А.О.</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Костюк Д.И.</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>ГПНВ</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Купалов О.А.</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>ИнТех</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Тихонов А.Ю.</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>17.02.2026</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>ИнТех</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Дмитриев И.Ю.</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>17.02.2026</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>ИнТех</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Куленин А.И.</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>МСБ</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Марущак А.И.</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Русэнерго"</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Давыдченко Д.Ю.</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>09.02.2026</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Русэнерго"</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Шершнев Е.М.</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>09.02.2026</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Мухаметгариев Р.Р.</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>06.02.2026</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Нухов Р.М.</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>05.02.2026</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Порошин А.В.</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>12.02.2026</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>22.02.2026</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Сатторов С.Р.</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>06.02.2026</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Камалов Р.Э</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>06.02.2026</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>ООО "Автоделюкс"</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Кармазин А.В.</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>11.02.2026</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>ООО "Газпромнефть  сервисные технологии"</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Меньщиков А.В.</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>22.02.2026</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>ООО "Газпромнефть Бизнес сервис"</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Мамбетов О.О.</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>ООО "УТТ-Югра"</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Дурбалов М.А.</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>ООО ЧОП "Отечество-С"</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Мездрин Е.В.</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>ООО ЧОП "Отечество-С"</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Дяминов Н.И.</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>ООО ЧОП "Отечество-С"</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Дяминов Д.И.</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>ООО ЧОП "Отечество-С"</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Носивец И.В.</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>17.02.2026</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>ООО ЧОП "Отечество-С"</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Корнеев В.Л.</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Угаров И.О.</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>22.02.2026</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Хохлов К.С.</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>13.02.2026</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>15.02.2026</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Шпилько Д.Н.</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>22.02.2026</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>23.02.2026</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Краморов Д.В.</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Гаус Н.В</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Береговая А.Ю.</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Налепа Т.Б.</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Яманаева А.М.</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Шведюк Е.Н.</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>02.02.2026</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Булах И.А.</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>16.02.2026</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Партнеры Томск</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Мейлах Н.Г</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>РК " Нефтесервис"</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Сурков А.Н.</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Сибирское управление Росехнадзора</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Степанов А.В.</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>03.02.2026</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>07.02.2026</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>СибМедЦентр</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Смолякова Н.В.</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>СибМедЦентр</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Евескин М.Ш.</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>ТИТЦ</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Сапега А.С.</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>ТИТЦ</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Ахмадишин З.М</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>ТИТЦ</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Гребнев В.Г.</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>ТИТЦ</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Мохнащеков А.В.</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>ТИТЦ</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Колесников А.Г.</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>УТТ-Югра</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Долгов Д.А.</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>УТТ-Югра</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Косарев Д.А.</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>ФБУ Омский ЦСМ</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Ожигова И.В.</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ФГБУ "ЦЛАТИ по СФО" </t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Проскурин В.А.</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>24.02.2026</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>

--- a/excel_files/report_2026-02-01_2026-02-28.xlsx
+++ b/excel_files/report_2026-02-01_2026-02-28.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G296"/>
+  <dimension ref="A1:G298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Колесов Ш.Р.</t>
+          <t>Сорокин И.Г.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>14.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>7500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -618,12 +618,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Сорокин И.Г.</t>
+          <t>Урюпов  А.Е.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>14.02.2026</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="6">
@@ -651,7 +651,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Урюпов  А.Е.</t>
+          <t>Колесов Ш.Р.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Софроненко Е.Д.</t>
+          <t>Русаков Д.Е.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="8">
@@ -717,17 +717,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Королева В.В.</t>
+          <t>Макаев И.Р.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>14.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
@@ -750,24 +750,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Федоренко Э.А.</t>
+          <t>Левин М.М.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="10">
@@ -783,17 +783,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Бабушкин Д.Б.</t>
+          <t>Бурдуков А.Н.</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Левин М.М.</t>
+          <t>Быковский В.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -849,24 +849,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Бурдуков А.Н.</t>
+          <t>Кондрашов С.С.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
           <t>25.02.2026</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F12" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="13">
@@ -882,24 +882,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Быковский В.</t>
+          <t>Шайхулов А.Р.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>9000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="14">
@@ -915,24 +915,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Лебедев В.С.</t>
+          <t>Смирнов Д.И.</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
           <t>18.02.2026</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="15">
@@ -948,24 +948,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Мартынов И.А.</t>
+          <t>Тишкин</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16">
@@ -981,7 +981,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Поликарпов Е.Ю.</t>
+          <t>Шеверов В.В.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1014,24 +1014,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Шайхулов А.Р.</t>
+          <t>Мартынов И.А.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
           <t>18.02.2026</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F17" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="18">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Смирнов Д.И.</t>
+          <t>Кондратьев О.А</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1057,14 +1057,14 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>7500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="19">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Тишкин</t>
+          <t>Филанчук Г.В.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
@@ -1113,24 +1113,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Шеверов В.В.</t>
+          <t>Трапезников А.С.</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="21">
@@ -1146,24 +1146,24 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Русаков К.Е.</t>
+          <t>Иванов А.Г.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="22">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Корнеев П.О.</t>
+          <t>Колобов С.В.</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1189,14 +1189,14 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>12500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="23">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Русаков Д.Е.</t>
+          <t>Раздобудько И.В.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
@@ -1245,24 +1245,24 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Соломенников Д.П.</t>
+          <t>Антонов А.В.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
           <t>18.02.2026</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>23.02.2026</t>
-        </is>
-      </c>
       <c r="F24" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="25">
@@ -1278,24 +1278,24 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Купчиков Д.А.</t>
+          <t>Опалинский М.В.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>9000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="26">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Федоров А.С.</t>
+          <t>Кутлияров А.П.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="27">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Гарифуллин А.Ф.</t>
+          <t>Соловьев Р.Н.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Гонина Е.Е.</t>
+          <t>Савинский С.В.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Ловкин С.И.</t>
+          <t>Якушин А.В.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="30">
@@ -1443,24 +1443,24 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Пивкин С.В.</t>
+          <t>Деденев В.Е.</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="31">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Целищев М.Ю.</t>
+          <t>Шатохин А.О.</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="32">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Павловский В.В.</t>
+          <t>Казанцев С.А.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33">
@@ -1542,24 +1542,24 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Конаков А.Н.</t>
+          <t>Гончаров А.С.</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="34">
@@ -1575,24 +1575,24 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Москвин В.В.</t>
+          <t>Ганеев А.Р.</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
           <t>18.02.2026</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F34" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="35">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Дудин Л.С.</t>
+          <t>Зозуля Ю.А.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="36">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Пукман В.В.</t>
+          <t>Ряполов Б.Н.</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
+          <t>04.02.2026</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
           <t>18.02.2026</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F36" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>5500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="37">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Корунец Д.А.</t>
+          <t>Будылдин П.С.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1684,14 +1684,14 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="38">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Мокеев Ю.В.</t>
+          <t>Зандер Д.Э.</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>12500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="39">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Кузнецов В.М.</t>
+          <t>Чудиновский А.О.</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1773,24 +1773,24 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Школин К.М.</t>
+          <t>Ловкин С.И.</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>9000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="41">
@@ -1811,19 +1811,19 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>08.02.2026</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="42">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Бляхер Е.</t>
+          <t>Целищев М.Ю.</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -1872,24 +1872,24 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Шайхиев И.Р.</t>
+          <t>Павловский В.В.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Отставных А.Н.</t>
+          <t>Конаков А.Н.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="45">
@@ -1938,24 +1938,24 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Юшков А.А.</t>
+          <t>Москвин В.В.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="46">
@@ -1971,24 +1971,24 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Щербак В.В.</t>
+          <t>Дудин Л.С.</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Сайнаков Д.П.</t>
+          <t>Пукман В.В.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="48">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Звягинцев А.В.</t>
+          <t>Корунец Д.А.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -2047,14 +2047,14 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>9000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Попов М.А.</t>
+          <t>Мокеев Ю.В.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="50">
@@ -2103,24 +2103,24 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Кондрашов С.С.</t>
+          <t>Кузнецов В.М.</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>12500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="51">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Новейченко А.А.</t>
+          <t>Школин К.М.</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -2146,14 +2146,14 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>12500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="52">
@@ -2169,24 +2169,24 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Бабаев Н.Н.</t>
+          <t>Пивкин С.В.</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>08.02.2026</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="53">
@@ -2202,24 +2202,24 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Макаев И.Р.</t>
+          <t>Бляхер Е.</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="54">
@@ -2235,24 +2235,24 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Петров Е.В.</t>
+          <t>Шайхиев И.Р.</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="55">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Чигвинцев М.А.</t>
+          <t>Корнеев П.О.</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -2278,14 +2278,14 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="56">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Константинов А.В.</t>
+          <t>Купчиков Д.А.</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Белозерцев А.А.</t>
+          <t>Федоров А.С.</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Шигаев Д.В.</t>
+          <t>Гарифуллин А.Ф.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
@@ -2400,24 +2400,24 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Бабаев Д.Н.</t>
+          <t>Гонина Е.Е.</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>12500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="60">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Мамец А.С.</t>
+          <t>Софроненко Е.Д.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -2466,24 +2466,24 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Соловьева П.А.</t>
+          <t>Королева В.В.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>14.02.2026</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="62">
@@ -2499,24 +2499,24 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Нестеров Н.Ю.</t>
+          <t>Федоренко Э.А.</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63">
@@ -2532,24 +2532,24 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Кондратьев О.А</t>
+          <t>Нестеров Н.Ю.</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
           <t>04.02.2026</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F63" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>12500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="64">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Филанчук Г.В.</t>
+          <t>Соловьева П.А.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -2598,24 +2598,24 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Трапезников А.С.</t>
+          <t>Мамец А.С.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="66">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Иванов А.Г.</t>
+          <t>Бабаев Д.Н.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>9000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="67">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Колобов С.В.</t>
+          <t>Шигаев Д.В.</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="68">
@@ -2697,24 +2697,24 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Раздобудько И.В.</t>
+          <t>Белозерцев А.А.</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="69">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Антонов А.В.</t>
+          <t>Константинов А.В.</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Опалинский М.В.</t>
+          <t>Чигвинцев М.А.</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="71">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Кутлияров А.П.</t>
+          <t>Петров Е.В.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2810,10 +2810,10 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>12500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="72">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Соловьев Р.Н.</t>
+          <t>Новейченко А.А.</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2839,14 +2839,14 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="73">
@@ -2862,24 +2862,24 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Савинский С.В.</t>
+          <t>Русаков К.Е.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="74">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Якушин А.В.</t>
+          <t>Попов М.А.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Деденев В.Е.</t>
+          <t>Звягинцев А.В.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2938,14 +2938,14 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="76">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Шатохин А.О.</t>
+          <t>Сайнаков Д.П.</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="77">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Казанцев С.А.</t>
+          <t>Отставных А.Н.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3027,24 +3027,24 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Гончаров А.С.</t>
+          <t>Соломенников Д.П.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="79">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Ганеев А.Р.</t>
+          <t>Поликарпов Е.Ю.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -3070,14 +3070,14 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="80">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Зозуля Ю.А.</t>
+          <t>Лебедев В.С.</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>12500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="81">
@@ -3126,24 +3126,24 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Ряполов Б.Н.</t>
+          <t>Бабушкин Д.Б.</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
           <t>04.02.2026</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>18.02.2026</t>
-        </is>
-      </c>
       <c r="F81" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>7500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="82">
@@ -3159,24 +3159,24 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Будылдин П.С.</t>
+          <t>Бабаев Н.Н.</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="83">
@@ -3192,24 +3192,24 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Зандер Д.Э.</t>
+          <t>Щербак В.В.</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>7500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="84">
@@ -3225,24 +3225,24 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Чудиновский А.О.</t>
+          <t>Юшков А.А.</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>5500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="85">
@@ -3291,24 +3291,24 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Замараев Д.А.</t>
+          <t>Априщенко П.А.</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>17.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>8500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="87">
@@ -3324,24 +3324,24 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Кабитов Д.А.</t>
+          <t>Кузнецов И.В.</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>17.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="88">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Априщенко П.А.</t>
+          <t>Черников В.П.</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -3390,24 +3390,24 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Кузнецов И.В.</t>
+          <t>Кабитов Д.А.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>17.02.2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="90">
@@ -3423,24 +3423,24 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Черников В.П.</t>
+          <t>Замараев Д.А.</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>17.02.2026</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>1000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="91">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Житник М.С.</t>
+          <t>Назаренко И.М.</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3499,14 +3499,14 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>14000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="93">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Назаренко И.М.</t>
+          <t>Мозговой О.А.</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -3532,14 +3532,14 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>5500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="94">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Бедняков Р.С.</t>
+          <t>Житник М.С.</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>20.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>4500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="95">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Мозговой О.А.</t>
+          <t>Бедняков Р.С.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>20.02.2026</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>14000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="96">
@@ -3621,24 +3621,24 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Сидельцев Д.М.</t>
+          <t>Марченко И.В.</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>15.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>7500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97">
@@ -3654,24 +3654,24 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Марченко И.В.</t>
+          <t>Сидельцев Д.М.</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>15.02.2026</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>500</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="98">
@@ -3687,24 +3687,24 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Шведюк Е.Н.</t>
+          <t>Мейлах Н.Г.</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>14.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>5500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="99">
@@ -3852,24 +3852,24 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Георгиев А.А.</t>
+          <t>Шведюк Е.Н.</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>14.02.2026</t>
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>1500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="104">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Стешенко Е.А.</t>
+          <t>Георгиев А.А.</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -3895,14 +3895,14 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="105">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Созанович Е.А.</t>
+          <t>Стешенко Е.А.</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Благодатных С.Н.</t>
+          <t>Созанович Е.А.</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Чернова Т.В.</t>
+          <t>Благодатных С.Н.</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Мейлах Н.Г.</t>
+          <t>Чернова Т.В.</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Сафаралеева С.Х.</t>
+          <t>Налепа Т.Б.</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>14.02.2026</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>14000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="111">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Налепа Т.Б.</t>
+          <t>Сафаралеева С.Х.</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>14.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>7500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="112">
@@ -4210,29 +4210,29 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>АНО ДПО "ЮУЦ"</t>
+          <t xml:space="preserve"> Сервис центр ЭПУ</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Афанасьева А.А.</t>
+          <t>Попов</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>5500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115">
@@ -4243,29 +4243,29 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Автоматизация</t>
+          <t>АНО ДПО "ЮУЦ"</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Коваленко Е.А.</t>
+          <t>Афанасьева А.А.</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>1500</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="116">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Ловицкий А.А.</t>
+          <t>Рогачевских Ю.С.</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -4314,24 +4314,24 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Коновалова Е.Г.</t>
+          <t>Талицких М.В.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>10.02.2026</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>1500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="118">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Платонов С.В.</t>
+          <t>Манашев Р.Ю.</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>10.02.2026</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="F118" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>14000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="119">
@@ -4380,24 +4380,24 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Солякин С.В.</t>
+          <t>Нигматьянов А.И.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F119" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="120">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Давыдов Д.А.</t>
+          <t>Попов Е.А.</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>10.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="F120" s="3" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>9500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="121">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Спиридонов Я.Э.</t>
+          <t>Жильцов Д.В.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -4479,24 +4479,24 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Асылгареев М.Р.</t>
+          <t>Коновалова Е.Г.</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="123">
@@ -4512,24 +4512,24 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Юн В.В.</t>
+          <t>Ловицкий А.А.</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>10.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>9500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="124">
@@ -4545,24 +4545,24 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Талицких М.В.</t>
+          <t>Коваленко Е.А.</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>10.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>9500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="125">
@@ -4578,24 +4578,24 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Манашев Р.Ю.</t>
+          <t>Логинов В.А.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>10.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F125" s="3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>9500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="126">
@@ -4611,24 +4611,24 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Шихалев В.И.</t>
+          <t>Казанцева А.А.</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="127">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Попов Е.А.</t>
+          <t>Спиридонов Я.Э.</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Жильцов Д.В.</t>
+          <t>Асылгареев М.Р.</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -4710,24 +4710,24 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Рогачевских Ю.С.</t>
+          <t>Платонов С.В.</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="130">
@@ -4743,24 +4743,24 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Нигматьянов А.И.</t>
+          <t>Шихалев В.И.</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F130" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>1500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="131">
@@ -4776,24 +4776,24 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Казанцева А.А.</t>
+          <t>Солякин С.В.</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>1500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="132">
@@ -4842,24 +4842,24 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Логинов В.А.</t>
+          <t>Давыдов Д.А.</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>10.02.2026</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>1500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="134">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ГПН-В</t>
+          <t>ГПН-Автоматизация</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Сизов И.В.</t>
+          <t>Юн В.В.</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>10.02.2026</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="F134" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>2000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="135">
@@ -4908,24 +4908,24 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Талынов Н.С.</t>
+          <t>Хасанов А.А.</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="136">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Дудин Л.С.</t>
+          <t>Колобов С.В.</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Колобов С.В.</t>
+          <t>Стишенко О.И</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="F137" s="3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>5500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="138">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Чигвинцев М.А.</t>
+          <t>Попов М.А.</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F138" s="3" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="139">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Воронецкий Д.В.</t>
+          <t>Стальмаков О.В.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -5050,14 +5050,14 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>14000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="140">
@@ -5106,24 +5106,24 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Попов М.А.</t>
+          <t>Трубинов А.С.</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="142">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Стишенко О.И</t>
+          <t>Звягинцев  А.В.</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -5153,10 +5153,10 @@
         </is>
       </c>
       <c r="F142" s="3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>14000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="143">
@@ -5205,24 +5205,24 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Стальмаков О.В.</t>
+          <t>Гончаров А.С.</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F144" s="3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>2000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="145">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Звягинцев  А.В.</t>
+          <t>Малко Э.В.</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="F145" s="3" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>5500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="146">
@@ -5271,24 +5271,24 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Кузнецов В.М.</t>
+          <t>Яровой Д.В.</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F146" s="3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>9000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="147">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Яровой Д.В.</t>
+          <t>Андреев М.А.</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -5318,10 +5318,10 @@
         </is>
       </c>
       <c r="F147" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="148">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Трубинов А.С.</t>
+          <t>Дудин Л.С.</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="F148" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>2000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="149">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Будылдин П.С.</t>
+          <t>Левин М.М.</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="F149" s="3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>14000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="150">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Русаков Д.Е.</t>
+          <t>Чигвинцев М.А.</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F150" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>2000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="151">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Хасанов А.А.</t>
+          <t>Русаков Д.Е.</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Назаров Р.Р.</t>
+          <t>Купчиков Д.А.</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="F152" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>14000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="153">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Бабаев Д.Н.</t>
+          <t>Талынов Н.С.</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -5512,14 +5512,14 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="154">
@@ -5535,24 +5535,24 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Левин М.М.</t>
+          <t>Кузнецов В.М.</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
           <t>18.02.2026</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
       <c r="F154" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>5500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="155">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Андреев М.А.</t>
+          <t>Петров Д.Е.</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Гончаров А.С.</t>
+          <t>Воронецкий Д.В.</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="F157" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="158">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Петров Д.Е.</t>
+          <t>Назаров Р.Р.</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Малко Э.В.</t>
+          <t>Будылдин П.С.</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Купчиков Д.А.</t>
+          <t>Бабаев Д.Н.</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -5743,14 +5743,14 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F160" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>12500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="161">
@@ -5761,29 +5761,29 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>ГПН-ИТО</t>
+          <t>ГПН-В</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Филимонов К.В.</t>
+          <t>Сизов И.В.</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F161" s="3" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>9500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="162">
@@ -5799,24 +5799,24 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Казанцев Д.А.</t>
+          <t>Филимонов К.В.</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="F162" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>2000</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="163">
@@ -5827,29 +5827,29 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Снабжение</t>
+          <t>ГПН-ИТО</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Черников В.П.</t>
+          <t>Казанцев Д.А.</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="164">
@@ -5893,29 +5893,29 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>ГПН-Энергосистемы</t>
+          <t>ГПН-Снабжение</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Власенко В.Н.</t>
+          <t>Черников В.П.</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="166">
@@ -5931,24 +5931,24 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Варламов В.А.</t>
+          <t>Сеник У.Н.</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="F166" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="167">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Телицын А.П.</t>
+          <t>Власенко В.Н.</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -6030,24 +6030,24 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Сеник У.Н.</t>
+          <t>Варламов В.А.</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="170">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>ГПНВ</t>
+          <t>ГПН-Энергосистемы</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Сулимский Д.М.</t>
+          <t>Телицын А.П.</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>19.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="F170" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="171">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Шигаев Д.В.</t>
+          <t>Ардашов А.Г.</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="F171" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>12500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="172">
@@ -6129,24 +6129,24 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Купалов Д.А.</t>
+          <t>Шигаев Д.В.</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>9000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="173">
@@ -6162,24 +6162,24 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Ардашов А.Г.</t>
+          <t>Купалов Д.А.</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>2000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="174">
@@ -8373,24 +8373,24 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Богданович В.В.</t>
+          <t>Сулимский Д.М.</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>12.02.2026</t>
+          <t>19.02.2026</t>
         </is>
       </c>
       <c r="F240" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="241">
@@ -8406,17 +8406,17 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Толмачев М.И.</t>
+          <t>Богданович В.В.</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>26.02.2026</t>
+          <t>12.02.2026</t>
         </is>
       </c>
       <c r="F241" s="3" t="n">
@@ -8439,17 +8439,17 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Малахов П.В.</t>
+          <t>Толмачев М.И.</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>12.02.2026</t>
+          <t>26.02.2026</t>
         </is>
       </c>
       <c r="F242" s="3" t="n">
@@ -8472,24 +8472,24 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Мишин В.А.</t>
+          <t>Малахов П.В.</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>12.02.2026</t>
         </is>
       </c>
       <c r="F243" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="244">
@@ -8505,24 +8505,24 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Худорожко А.С.</t>
+          <t>Мишин В.А.</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F244" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>12500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="245">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Терентьев Д.А.</t>
+          <t>Худорожко А.С.</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="F245" s="3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G245" s="4" t="n">
-        <v>11000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="246">
@@ -8571,24 +8571,24 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Черепанов И.В.</t>
+          <t>Терентьев Д.А.</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="F246" s="3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="247">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Тимощенко Д.А.</t>
+          <t>Черепанов И.В.</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -8614,14 +8614,14 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="F247" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G247" s="4" t="n">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="248">
@@ -8637,24 +8637,24 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Попов А.А.</t>
+          <t>Тимощенко Д.А.</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="F248" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>12500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="249">
@@ -8670,24 +8670,24 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Сорокин А.А.</t>
+          <t>Попов А.А.</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>12.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F249" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>1000</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="250">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Кусков А.Ю.</t>
+          <t>Сорокин А.А.</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -8736,24 +8736,24 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Шаталов А.О.</t>
+          <t>Кусков А.Ю.</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>12.02.2026</t>
         </is>
       </c>
       <c r="F251" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="252">
@@ -8769,24 +8769,24 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Костюк Д.И.</t>
+          <t>Шаталов А.О.</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F252" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="253">
@@ -8802,24 +8802,24 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Купалов О.А.</t>
+          <t>Костюк Д.И.</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>04.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="F253" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>12500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="254">
@@ -8830,29 +8830,29 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>ИнТех</t>
+          <t>ГПНВ</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Дмитриев И.Ю.</t>
+          <t>Купалов О.А.</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>04.02.2026</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>17.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F254" s="3" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>8500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="255">
@@ -8901,24 +8901,24 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Куленин А.И.</t>
+          <t>Дмитриев И.Ю.</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>17.02.2026</t>
         </is>
       </c>
       <c r="F256" s="3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>2500</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="257">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>МСБ</t>
+          <t>ИнТех</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Марущак А.И.</t>
+          <t>Куленин А.И.</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="F257" s="3" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>14000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="258">
@@ -8962,17 +8962,17 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>ООО " Русэнерго"</t>
+          <t>МСБ</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Шершнев Е.М.</t>
+          <t>Марущак А.И.</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>09.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="F258" s="3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>10000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="259">
@@ -8995,29 +8995,29 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>ООО " Русэнерго"</t>
+          <t xml:space="preserve">ООО </t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Давыдченко Д.Ю.</t>
+          <t>Шарипов</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>09.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>02.02.2026</t>
         </is>
       </c>
       <c r="F259" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G259" s="4" t="n">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="260">
@@ -9028,29 +9028,29 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>ООО " Уралтрубопроводстройпроект"</t>
+          <t>ООО " Русэнерго"</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Нухов Р.М.</t>
+          <t>Давыдченко Д.Ю.</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>09.02.2026</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F260" s="3" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="261">
@@ -9061,29 +9061,29 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>ООО " Уралтрубопроводстройпроект"</t>
+          <t>ООО " Русэнерго"</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Камалов Р.Э</t>
+          <t>Шершнев Е.М.</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>06.02.2026</t>
+          <t>09.02.2026</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F261" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="262">
@@ -9132,24 +9132,24 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Мухаметгариев Р.Р.</t>
+          <t>Порошин А.В.</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>06.02.2026</t>
+          <t>12.02.2026</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="F263" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G263" s="4" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="264">
@@ -9165,24 +9165,24 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Порошин А.В.</t>
+          <t>Нухов Р.М.</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>12.02.2026</t>
+          <t>05.02.2026</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="F264" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>5500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="265">
@@ -9193,29 +9193,29 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>ООО "Автоделюкс"</t>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Кармазин А.В.</t>
+          <t>Камалов Р.Э</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>11.02.2026</t>
+          <t>06.02.2026</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="F265" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G265" s="4" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="266">
@@ -9226,29 +9226,29 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>ООО "Газпромнефть  сервисные технологии"</t>
+          <t>ООО " Уралтрубопроводстройпроект"</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Меньщиков А.В.</t>
+          <t>Мухаметгариев Р.Р.</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>06.02.2026</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="F266" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="267">
@@ -9259,29 +9259,29 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>ООО "Газпромнефть Бизнес сервис"</t>
+          <t>ООО "Автоделюкс"</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Мамбетов О.О.</t>
+          <t>Кармазин А.В.</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>11.02.2026</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="F267" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>5500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="268">
@@ -9292,29 +9292,29 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>ООО "УТТ-Югра"</t>
+          <t>ООО "Газпромнефть  сервисные технологии"</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Дурбалов М.А.</t>
+          <t>Меньщиков А.В.</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="F268" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="269">
@@ -9325,17 +9325,17 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>ООО ЧОП "Отечество-С"</t>
+          <t>ООО "Газпромнефть Бизнес сервис"</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Дяминов Д.И.</t>
+          <t>Мамбетов О.О.</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>18.02.2026</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="F269" s="3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G269" s="4" t="n">
-        <v>14000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="270">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>ООО ЧОП "Отечество-С"</t>
+          <t>ООО "УТТ-Югра"</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Носивец И.В.</t>
+          <t>Дурбалов М.А.</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -9373,14 +9373,14 @@
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>17.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F270" s="3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>8500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="271">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Корнеев В.Л.</t>
+          <t>Мездрин Е.В.</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Мездрин Е.В.</t>
+          <t>Дяминов Н.И.</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Дяминов Н.И.</t>
+          <t>Дяминов Д.И.</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Партнеры Томск</t>
+          <t>ООО ЧОП "Отечество-С"</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Гаус Н.В</t>
+          <t>Носивец И.В.</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -9505,14 +9505,14 @@
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>17.02.2026</t>
         </is>
       </c>
       <c r="F274" s="3" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>14000</v>
+        <v>8500</v>
       </c>
     </row>
     <row r="275">
@@ -9523,29 +9523,29 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Партнеры Томск</t>
+          <t>ООО ЧОП "Отечество-С"</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Хохлов К.С.</t>
+          <t>Корнеев В.Л.</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>13.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>15.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F275" s="3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G275" s="4" t="n">
-        <v>1500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="276">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Угаров И.О.</t>
+          <t>Гаус Н.В</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="F276" s="3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>3500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="277">
@@ -9594,24 +9594,24 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Береговая А.Ю.</t>
+          <t>Хохлов К.С.</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>13.02.2026</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>15.02.2026</t>
         </is>
       </c>
       <c r="F277" s="3" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G277" s="4" t="n">
-        <v>14000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="278">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Булах И.А.</t>
+          <t>Налепа Т.Б.</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>16.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -9641,10 +9641,10 @@
         </is>
       </c>
       <c r="F278" s="3" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>6500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="279">
@@ -9660,24 +9660,24 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Шпилько Д.Н.</t>
+          <t>Булах И.А.</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>16.02.2026</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F279" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G279" s="4" t="n">
-        <v>1000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="280">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Мейлах Н.Г</t>
+          <t>Краморов Д.В.</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Краморов Д.В.</t>
+          <t>Угаров И.О.</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="F281" s="3" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G281" s="4" t="n">
-        <v>14000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="282">
@@ -9759,24 +9759,24 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Налепа Т.Б.</t>
+          <t>Шпилько Д.Н.</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="F282" s="3" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="283">
@@ -9787,29 +9787,29 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>РК " Нефтесервис"</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Сурков А.Н.</t>
+          <t>Мейлах Н.Г</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>24.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F283" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="284">
@@ -9820,29 +9820,29 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Сервис центр ЭПУ</t>
+          <t>Партнеры Томск</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Чумачкова М.С.</t>
+          <t>Береговая А.Ю.</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>22.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>23.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F284" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="285">
@@ -9853,29 +9853,29 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Сибирское управление Росехнадзора</t>
+          <t>РК " Нефтесервис"</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Степанов А.В.</t>
+          <t>Сурков А.Н.</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>24.02.2026</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>25.02.2026</t>
         </is>
       </c>
       <c r="F285" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G285" s="4" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="286">
@@ -9886,29 +9886,29 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>СибМедЦентр</t>
+          <t>Сервис центр ЭПУ</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Смолякова Н.В.</t>
+          <t>Чумачкова М.С.</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>22.02.2026</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>23.02.2026</t>
         </is>
       </c>
       <c r="F286" s="3" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="287">
@@ -9919,29 +9919,29 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>СибМедЦентр</t>
+          <t>Сибирское управление Росехнадзора</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Евескин М.Ш.</t>
+          <t>Степанов А.В.</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>03.02.2026</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="F287" s="3" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G287" s="4" t="n">
-        <v>14000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="288">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>ТИТЦ</t>
+          <t>СибМедЦентр</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Гребнев В.Г.</t>
+          <t>Смолякова Н.В.</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -9985,12 +9985,12 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>ТИТЦ</t>
+          <t>СибМедЦентр</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Мохнащеков А.В.</t>
+          <t>Евескин М.Ш.</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Ахмадишин З.М</t>
+          <t>Сапега А.С.</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -10033,14 +10033,14 @@
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>01.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F290" s="3" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="291">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Сапега А.С.</t>
+          <t>Ахмадишин З.М</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -10066,14 +10066,14 @@
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>28.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="F291" s="3" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G291" s="4" t="n">
-        <v>14000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="292">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Колесников А.Г.</t>
+          <t>Мохнащеков А.В.</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -10117,12 +10117,12 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>УТТ-Югра</t>
+          <t>ТИТЦ</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Долгов Д.А.</t>
+          <t>Гребнев В.Г.</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -10150,12 +10150,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>УТТ-Югра</t>
+          <t>ТИТЦ</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Косарев Д.А.</t>
+          <t>Колесников А.Г.</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -10183,29 +10183,29 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>ФБУ Омский ЦСМ</t>
+          <t>УТТ-Югра</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Ожигова И.В.</t>
+          <t>Косарев Д.А.</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>18.02.2026</t>
+          <t>01.02.2026</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>28.02.2026</t>
         </is>
       </c>
       <c r="F295" s="3" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G295" s="4" t="n">
-        <v>4000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="296">
@@ -10216,28 +10216,94 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
+          <t>УТТ-Югра</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Долгов Д.А.</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>01.02.2026</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G296" s="4" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>ФБУ Омский ЦСМ</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Ожигова И.В.</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>18.02.2026</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>25.02.2026</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G297" s="4" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Шингинское</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
           <t>ФГБУ "ЦЛАТИ по СФО"</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr">
+      <c r="C298" s="2" t="inlineStr">
         <is>
           <t>Проскурин В.А.</t>
         </is>
       </c>
-      <c r="D296" s="3" t="inlineStr">
+      <c r="D298" s="3" t="inlineStr">
         <is>
           <t>24.02.2026</t>
         </is>
       </c>
-      <c r="E296" s="3" t="inlineStr">
-        <is>
-          <t>28.02.2026</t>
-        </is>
-      </c>
-      <c r="F296" s="3" t="n">
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>28.02.2026</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G296" s="4" t="n">
+      <c r="G298" s="4" t="n">
         <v>2500</v>
       </c>
     </row>
